--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484374_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484374_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.9072</v>
+        <v>6.4937</v>
       </c>
       <c r="E2" t="n">
-        <v>4.2767</v>
+        <v>4.0538</v>
       </c>
       <c r="F2" t="n">
-        <v>2.6305</v>
+        <v>2.4399</v>
       </c>
       <c r="G2" t="n">
         <v>1.9768</v>
@@ -610,13 +610,13 @@
         <v>1.5627</v>
       </c>
       <c r="S2" t="n">
-        <v>1.8071</v>
+        <v>1.3936</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5973000000000001</v>
+        <v>0.3744</v>
       </c>
       <c r="U2" t="n">
-        <v>1.2098</v>
+        <v>1.0192</v>
       </c>
       <c r="V2" t="n">
         <v>2.5372</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>T. RAMIS NIELL</t>
+          <t>L. HUGUET CARRASCO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.087</v>
+        <v>1.3091</v>
       </c>
       <c r="E3" t="n">
-        <v>2.4333</v>
+        <v>0.8381999999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6536999999999999</v>
+        <v>0.4709</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1417</v>
+        <v>1.767</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.1011</v>
+        <v>-0.0133</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2428</v>
+        <v>1.7803</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.3925</v>
+        <v>0.7631</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.3658</v>
+        <v>-0.6127</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.0266</v>
+        <v>1.3758</v>
       </c>
       <c r="M3" t="n">
-        <v>0.5342</v>
+        <v>1.0039</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2648</v>
+        <v>0.5994</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2694</v>
+        <v>0.4045</v>
       </c>
       <c r="P3" t="n">
-        <v>0.7814</v>
+        <v>0.3907</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.7814</v>
+        <v>0.3907</v>
       </c>
       <c r="S3" t="n">
-        <v>2.8951</v>
+        <v>0.2153</v>
       </c>
       <c r="T3" t="n">
-        <v>2.8258</v>
+        <v>0.075</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0693</v>
+        <v>0.1402</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.7312</v>
+        <v>-1.0639</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.7312</v>
+        <v>-1.0639</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>I. MARTINEZ MESEGUER</t>
+          <t>T. RAMIS NIELL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.9878</v>
+        <v>1.2203</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.1132</v>
+        <v>0.5121</v>
       </c>
       <c r="F4" t="n">
-        <v>2.101</v>
+        <v>0.7082000000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.7171999999999999</v>
+        <v>0.1417</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.5818</v>
+        <v>-0.1011</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8646</v>
+        <v>0.2428</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.2081</v>
+        <v>-0.3925</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.669</v>
+        <v>-0.3658</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4609</v>
+        <v>-0.0266</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.5091</v>
+        <v>0.5342</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.9127</v>
+        <v>0.2648</v>
       </c>
       <c r="O4" t="n">
-        <v>0.4037</v>
+        <v>0.2694</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.9767</v>
+        <v>0.7814</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.9301</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.9534</v>
+        <v>0.7814</v>
       </c>
       <c r="S4" t="n">
-        <v>2.9846</v>
+        <v>1.0284</v>
       </c>
       <c r="T4" t="n">
-        <v>1.1971</v>
+        <v>0.9046</v>
       </c>
       <c r="U4" t="n">
-        <v>1.7875</v>
+        <v>0.1238</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6971000000000001</v>
+        <v>-0.7312</v>
       </c>
       <c r="W4" t="n">
-        <v>1.8279</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.1309</v>
+        <v>-0.7312</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>L. HUGUET CARRASCO</t>
+          <t>I. MARTINEZ MESEGUER</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8363</v>
+        <v>0.8273</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4743</v>
+        <v>-0.5383</v>
       </c>
       <c r="F5" t="n">
-        <v>0.362</v>
+        <v>1.3656</v>
       </c>
       <c r="G5" t="n">
-        <v>1.767</v>
+        <v>-0.7171999999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.0133</v>
+        <v>-1.5818</v>
       </c>
       <c r="I5" t="n">
-        <v>1.7803</v>
+        <v>0.8646</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7631</v>
+        <v>-0.2081</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.6127</v>
+        <v>-0.669</v>
       </c>
       <c r="L5" t="n">
-        <v>1.3758</v>
+        <v>0.4609</v>
       </c>
       <c r="M5" t="n">
-        <v>1.0039</v>
+        <v>-0.5091</v>
       </c>
       <c r="N5" t="n">
-        <v>0.5994</v>
+        <v>-0.9127</v>
       </c>
       <c r="O5" t="n">
-        <v>0.4045</v>
+        <v>0.4037</v>
       </c>
       <c r="P5" t="n">
-        <v>0.3907</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-2.9301</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3907</v>
+        <v>1.9534</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2575</v>
+        <v>1.8241</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2888</v>
+        <v>0.772</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0313</v>
+        <v>1.0522</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.0639</v>
+        <v>0.6971000000000001</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.8279</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.0639</v>
+        <v>-1.1309</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.2995</v>
+        <v>-0.3207</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.3894</v>
+        <v>-0.3289</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0898</v>
+        <v>0.0081</v>
       </c>
       <c r="G6" t="n">
         <v>0.429</v>
@@ -922,13 +922,13 @@
         <v>0.3907</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1425</v>
+        <v>-0.1637</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.121</v>
+        <v>-0.0605</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0215</v>
+        <v>-0.1032</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.7087</v>
+        <v>-1.1949</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.4032</v>
+        <v>-0.8077</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3055</v>
+        <v>-0.3872</v>
       </c>
       <c r="G7" t="n">
         <v>-0.5937</v>
@@ -1000,13 +1000,13 @@
         <v>0.1953</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6664</v>
+        <v>0.1802</v>
       </c>
       <c r="T7" t="n">
-        <v>0.5531</v>
+        <v>0.1486</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1133</v>
+        <v>0.0316</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S. PONS AVECILLAS</t>
+          <t>G. CATANY BIGAS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.7686</v>
+        <v>-1.2865</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.6641</v>
+        <v>-2.1401</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.1045</v>
+        <v>0.8536</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.3103</v>
+        <v>-1.5482</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3528</v>
+        <v>-0.6718</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.9576</v>
+        <v>-0.8764</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1227</v>
+        <v>-1.174</v>
       </c>
       <c r="K8" t="n">
-        <v>0.6754</v>
+        <v>0.1061</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.5527</v>
+        <v>-1.2801</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.433</v>
+        <v>-0.3743</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.0281</v>
+        <v>-0.7779</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.4049</v>
+        <v>0.4037</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.586</v>
+        <v>1.1721</v>
       </c>
       <c r="Q8" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R8" t="n">
-        <v>0.3907</v>
+        <v>2.1488</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1277</v>
+        <v>0.6074000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1899</v>
+        <v>0.0105</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0622</v>
+        <v>0.5969</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-1.5178</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.5178</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>E. ZUSTOVICH</t>
+          <t>S. PONS AVECILLAS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,58 +1111,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.2617</v>
+        <v>-1.7003</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.4321</v>
+        <v>-0.7047</v>
       </c>
       <c r="F9" t="n">
-        <v>1.1704</v>
+        <v>-0.9956</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.0414</v>
+        <v>-1.3103</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.1379</v>
+        <v>-0.3528</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.9035</v>
+        <v>-0.9576</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.9616</v>
+        <v>0.1227</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.6539</v>
+        <v>0.6754</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.3077</v>
+        <v>-0.5527</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.07969999999999999</v>
+        <v>-1.433</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.484</v>
+        <v>-1.0281</v>
       </c>
       <c r="O9" t="n">
-        <v>0.4043</v>
+        <v>-0.4049</v>
       </c>
       <c r="P9" t="n">
-        <v>0.586</v>
+        <v>-0.586</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R9" t="n">
-        <v>0.586</v>
+        <v>0.3907</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1937</v>
+        <v>0.1961</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4704</v>
+        <v>0.1493</v>
       </c>
       <c r="U9" t="n">
-        <v>0.6641</v>
+        <v>0.0467</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. BAUZA MEDINA</t>
+          <t>J. REDA COLL</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.9128</v>
+        <v>-2.109</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.1081</v>
+        <v>-1.3921</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.8048</v>
+        <v>-0.7169</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.1549</v>
+        <v>2.1043</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.9658</v>
+        <v>2.0356</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1891</v>
+        <v>0.0687</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.9401</v>
+        <v>1.7848</v>
       </c>
       <c r="K10" t="n">
-        <v>-2.021</v>
+        <v>1.9852</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0809</v>
+        <v>-0.2004</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.2148</v>
+        <v>0.3195</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0553</v>
+        <v>0.0504</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.27</v>
+        <v>0.269</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.3907</v>
+        <v>-2.1488</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9767</v>
+        <v>-2.9301</v>
       </c>
       <c r="R10" t="n">
-        <v>0.586</v>
+        <v>0.7814</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2454</v>
+        <v>0.0626</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4099</v>
+        <v>-0.2468</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1645</v>
+        <v>0.3094</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.1219</v>
+        <v>-2.1271</v>
       </c>
       <c r="W10" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.3405</v>
+        <v>-2.1271</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. REDA COLL</t>
+          <t>E. ZUSTOVICH</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.0074</v>
+        <v>-2.3041</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.0999</v>
+        <v>-3.311</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.9075</v>
+        <v>1.007</v>
       </c>
       <c r="G11" t="n">
-        <v>2.1043</v>
+        <v>-3.0414</v>
       </c>
       <c r="H11" t="n">
-        <v>2.0356</v>
+        <v>-2.1379</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0687</v>
+        <v>-0.9035</v>
       </c>
       <c r="J11" t="n">
-        <v>1.7848</v>
+        <v>-2.9616</v>
       </c>
       <c r="K11" t="n">
-        <v>1.9852</v>
+        <v>-1.6539</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.2004</v>
+        <v>-1.3077</v>
       </c>
       <c r="M11" t="n">
-        <v>0.3195</v>
+        <v>-0.07969999999999999</v>
       </c>
       <c r="N11" t="n">
-        <v>0.0504</v>
+        <v>-0.484</v>
       </c>
       <c r="O11" t="n">
-        <v>0.269</v>
+        <v>0.4043</v>
       </c>
       <c r="P11" t="n">
-        <v>-2.1488</v>
+        <v>0.586</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.9301</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.7814</v>
+        <v>0.586</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.8358</v>
+        <v>0.1513</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.9546</v>
+        <v>-0.3494</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1187</v>
+        <v>0.5007</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.1271</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.1271</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>G. CATANY BIGAS</t>
+          <t>A. BAUZA MEDINA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.3273</v>
+        <v>-2.7651</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.6362</v>
+        <v>-1.9058</v>
       </c>
       <c r="F12" t="n">
-        <v>0.3089</v>
+        <v>-0.8592</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.5482</v>
+        <v>-2.1549</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.6718</v>
+        <v>-1.9658</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.8764</v>
+        <v>-0.1891</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.174</v>
+        <v>-1.9401</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1061</v>
+        <v>-2.021</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.2801</v>
+        <v>0.0809</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.3743</v>
+        <v>-0.2148</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.7779</v>
+        <v>0.0553</v>
       </c>
       <c r="O12" t="n">
-        <v>0.4037</v>
+        <v>-0.27</v>
       </c>
       <c r="P12" t="n">
-        <v>1.1721</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q12" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R12" t="n">
-        <v>2.1488</v>
+        <v>0.586</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.4333</v>
+        <v>-0.0977</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.4855</v>
+        <v>-0.2077</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0522</v>
+        <v>0.11</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.5178</v>
+        <v>-0.1219</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.5178</v>
+        <v>-1.3405</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.0205</v>
+        <v>-3.7504</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.4491</v>
+        <v>-1.4785</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.5714</v>
+        <v>-2.2719</v>
       </c>
       <c r="G13" t="n">
         <v>-3.8398</v>
@@ -1468,13 +1468,13 @@
         <v>0.9767</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.9035</v>
+        <v>0.3667</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.8335</v>
+        <v>0.137</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0699</v>
+        <v>0.2297</v>
       </c>
       <c r="V13" t="n">
         <v>-0.2772</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-6.488200000000001</v>
+        <v>-5.580599999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>-8.111000000000001</v>
+        <v>-7.203000000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>1.622600000000001</v>
+        <v>1.6225</v>
       </c>
       <c r="G14" t="n">
         <v>-6.7867</v>
@@ -1516,13 +1516,13 @@
         <v>-6.7896</v>
       </c>
       <c r="I14" t="n">
-        <v>0.002899999999999459</v>
+        <v>0.002900000000000347</v>
       </c>
       <c r="J14" t="n">
         <v>-3.1926</v>
       </c>
       <c r="K14" t="n">
-        <v>-1.852099999999999</v>
+        <v>-1.8521</v>
       </c>
       <c r="L14" t="n">
         <v>-1.3404</v>
@@ -1546,13 +1546,13 @@
         <v>10.7438</v>
       </c>
       <c r="S14" t="n">
-        <v>4.856599999999999</v>
+        <v>5.7643</v>
       </c>
       <c r="T14" t="n">
-        <v>0.7995</v>
+        <v>1.707000000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>4.0571</v>
+        <v>4.0572</v>
       </c>
       <c r="V14" t="n">
         <v>-2.6048</v>
@@ -1561,7 +1561,7 @@
         <v>6.979600000000001</v>
       </c>
       <c r="X14" t="n">
-        <v>-9.5846</v>
+        <v>-9.584600000000002</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>8.428599999999999</v>
+        <v>8.19</v>
       </c>
       <c r="E15" t="n">
-        <v>7.1542</v>
+        <v>7.0531</v>
       </c>
       <c r="F15" t="n">
-        <v>1.2744</v>
+        <v>1.1368</v>
       </c>
       <c r="G15" t="n">
         <v>7.8742</v>
@@ -1624,13 +1624,13 @@
         <v>2.1488</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.0083</v>
+        <v>-0.247</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.4483</v>
+        <v>-0.5494</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4399</v>
+        <v>0.3024</v>
       </c>
       <c r="V15" t="n">
         <v>-0.6093</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.2131</v>
+        <v>4.2196</v>
       </c>
       <c r="E16" t="n">
-        <v>3.2223</v>
+        <v>3.1211</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9909</v>
+        <v>1.0985</v>
       </c>
       <c r="G16" t="n">
         <v>4.3841</v>
@@ -1702,13 +1702,13 @@
         <v>1.7581</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.585</v>
+        <v>-0.5785</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.5226</v>
+        <v>-0.6237</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0624</v>
+        <v>0.0452</v>
       </c>
       <c r="V16" t="n">
         <v>0.6093</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.5759</v>
+        <v>3.9052</v>
       </c>
       <c r="E17" t="n">
-        <v>2.8626</v>
+        <v>3.166</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7133</v>
+        <v>0.7392</v>
       </c>
       <c r="G17" t="n">
         <v>3.1314</v>
@@ -1780,13 +1780,13 @@
         <v>1.5627</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1415</v>
+        <v>0.1877</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5309</v>
+        <v>-0.2276</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3894</v>
+        <v>0.4153</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1012</v>
+        <v>0.026</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.682</v>
+        <v>-1.7831</v>
       </c>
       <c r="F18" t="n">
-        <v>1.7832</v>
+        <v>1.8091</v>
       </c>
       <c r="G18" t="n">
         <v>-1.8263</v>
@@ -1858,13 +1858,13 @@
         <v>1.1721</v>
       </c>
       <c r="S18" t="n">
-        <v>0.7554999999999999</v>
+        <v>0.6803</v>
       </c>
       <c r="T18" t="n">
-        <v>0.2037</v>
+        <v>0.1026</v>
       </c>
       <c r="U18" t="n">
-        <v>0.5518</v>
+        <v>0.5777</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.7237</v>
+        <v>-0.8507</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.7214</v>
+        <v>-1.227</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.0023</v>
+        <v>0.3763</v>
       </c>
       <c r="G19" t="n">
         <v>-0.5543</v>
@@ -1936,13 +1936,13 @@
         <v>1.1721</v>
       </c>
       <c r="S19" t="n">
-        <v>0.6119</v>
+        <v>0.4849</v>
       </c>
       <c r="T19" t="n">
-        <v>0.6219</v>
+        <v>0.1164</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.01</v>
+        <v>0.3686</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. MONTSERRAT SERRA</t>
+          <t>M. VANCEA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.1439</v>
+        <v>-0.9779</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.6681</v>
+        <v>-2.6304</v>
       </c>
       <c r="F20" t="n">
-        <v>2.5242</v>
+        <v>1.6525</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.1445</v>
+        <v>-1.2833</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.4001</v>
+        <v>-2.8601</v>
       </c>
       <c r="I20" t="n">
-        <v>0.2556</v>
+        <v>1.5768</v>
       </c>
       <c r="J20" t="n">
-        <v>-2.4727</v>
+        <v>-1.8623</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.92</v>
+        <v>-2.6312</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.5527</v>
+        <v>0.7688</v>
       </c>
       <c r="M20" t="n">
-        <v>1.3282</v>
+        <v>0.579</v>
       </c>
       <c r="N20" t="n">
-        <v>0.5199</v>
+        <v>-0.2289</v>
       </c>
       <c r="O20" t="n">
-        <v>0.8083</v>
+        <v>0.8079</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.7814</v>
+        <v>0.7814</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R20" t="n">
-        <v>1.1721</v>
+        <v>1.7581</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.9911</v>
+        <v>-1.3076</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.0151</v>
+        <v>-0.9002</v>
       </c>
       <c r="U20" t="n">
-        <v>0.024</v>
+        <v>-0.4074</v>
       </c>
       <c r="V20" t="n">
-        <v>1.7731</v>
+        <v>0.8317</v>
       </c>
       <c r="W20" t="n">
-        <v>1.7731</v>
+        <v>1.1089</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. VANCEA</t>
+          <t>M. MONTSERRAT SERRA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.5406</v>
+        <v>-1.0986</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.7315</v>
+        <v>-3.567</v>
       </c>
       <c r="F21" t="n">
-        <v>1.1908</v>
+        <v>2.4684</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.2833</v>
+        <v>-1.1445</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.8601</v>
+        <v>-1.4001</v>
       </c>
       <c r="I21" t="n">
-        <v>1.5768</v>
+        <v>0.2556</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.8623</v>
+        <v>-2.4727</v>
       </c>
       <c r="K21" t="n">
-        <v>-2.6312</v>
+        <v>-1.92</v>
       </c>
       <c r="L21" t="n">
-        <v>0.7688</v>
+        <v>-0.5527</v>
       </c>
       <c r="M21" t="n">
-        <v>0.579</v>
+        <v>1.3282</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.2289</v>
+        <v>0.5199</v>
       </c>
       <c r="O21" t="n">
-        <v>0.8079</v>
+        <v>0.8083</v>
       </c>
       <c r="P21" t="n">
-        <v>0.7814</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R21" t="n">
-        <v>1.7581</v>
+        <v>1.1721</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.8704</v>
+        <v>-0.9458</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.0013</v>
+        <v>-0.914</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.869</v>
+        <v>-0.0318</v>
       </c>
       <c r="V21" t="n">
-        <v>0.8317</v>
+        <v>1.7731</v>
       </c>
       <c r="W21" t="n">
-        <v>1.1089</v>
+        <v>1.7731</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.1046</v>
+        <v>-2.6586</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.7674</v>
+        <v>-2.5652</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.3371</v>
+        <v>-0.0934</v>
       </c>
       <c r="G22" t="n">
         <v>-2.0889</v>
@@ -2170,13 +2170,13 @@
         <v>0.9767</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.6249</v>
+        <v>-1.1789</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.0756</v>
+        <v>-0.8734</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5493</v>
+        <v>-0.3055</v>
       </c>
       <c r="V22" t="n">
         <v>0.6093</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.3177</v>
+        <v>-2.9184</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.2912</v>
+        <v>-3.1901</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.0265</v>
+        <v>0.2717</v>
       </c>
       <c r="G23" t="n">
         <v>-1.7058</v>
@@ -2248,13 +2248,13 @@
         <v>0.9767</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.0026</v>
+        <v>-0.6032</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2888</v>
+        <v>-0.1877</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.7138</v>
+        <v>-0.4155</v>
       </c>
       <c r="V23" t="n">
         <v>-0.6093</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>6.488299999999999</v>
+        <v>7.836599999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.6225</v>
+        <v>-1.622600000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>8.110899999999999</v>
+        <v>9.459099999999999</v>
       </c>
       <c r="G24" t="n">
         <v>6.7866</v>
@@ -2326,13 +2326,13 @@
         <v>12.6974</v>
       </c>
       <c r="S24" t="n">
-        <v>-4.8564</v>
+        <v>-3.5081</v>
       </c>
       <c r="T24" t="n">
-        <v>-4.056999999999999</v>
+        <v>-4.057</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.7993999999999999</v>
+        <v>0.549</v>
       </c>
       <c r="V24" t="n">
         <v>2.6048</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484374_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484374_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X24"/>
+  <dimension ref="A1:Y24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-0.1773</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484374_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-1.0639</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484374_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-0.7312</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484374_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-1.1309</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484374_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484374_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484374_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-1.5178</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484374_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484374_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-2.1271</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484374_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>0</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484374_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-1.3405</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484374_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,11 @@
       <c r="X13" t="n">
         <v>-1.4959</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484374_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1628,7 @@
       <c r="X14" t="n">
         <v>-9.584600000000002</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-1.2186</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484374_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-0.6093</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484374_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-2.4373</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484374_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484374_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-1.2186</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484374_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-0.2772</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484374_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>0</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484374_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>0</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484374_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-1.2186</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484374_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,7 @@
       <c r="X24" t="n">
         <v>-6.9796</v>
       </c>
+      <c r="Y24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
